--- a/files/港岛-半山-雅盈峰.xlsx
+++ b/files/港岛-半山-雅盈峰.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="雅盈峰 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1002,7 +869,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1048,7 +915,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1240,7 +1107,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1286,7 +1153,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1378,7 +1245,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1424,7 +1291,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1470,7 +1337,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1516,7 +1383,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1562,7 +1429,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1608,7 +1475,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1654,7 +1521,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1700,7 +1567,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1746,7 +1613,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1792,7 +1659,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1838,7 +1705,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1884,7 +1751,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1930,7 +1797,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1976,7 +1843,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2022,7 +1889,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2068,7 +1935,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2114,7 +1981,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2160,7 +2027,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2206,7 +2073,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2252,7 +2119,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2298,7 +2165,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2344,7 +2211,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2390,7 +2257,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2436,7 +2303,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2482,7 +2349,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2528,7 +2395,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2574,7 +2441,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2620,7 +2487,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2666,7 +2533,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2712,7 +2579,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2758,7 +2625,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2804,7 +2671,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2850,7 +2717,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2896,7 +2763,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2942,7 +2809,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2988,7 +2855,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3034,7 +2901,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3080,7 +2947,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3126,7 +2993,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3172,7 +3039,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3218,7 +3085,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3264,7 +3131,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3310,7 +3177,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3356,7 +3223,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3402,7 +3269,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3448,7 +3315,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3494,7 +3361,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3540,7 +3407,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3586,7 +3453,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3632,7 +3499,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3678,7 +3545,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3724,7 +3591,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3770,7 +3637,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3816,7 +3683,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3862,7 +3729,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3908,7 +3775,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3954,7 +3821,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4000,7 +3867,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4046,7 +3913,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4092,7 +3959,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4138,7 +4005,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4184,7 +4051,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4230,7 +4097,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4276,7 +4143,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4322,7 +4189,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4368,7 +4235,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4414,7 +4281,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4460,7 +4327,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4506,7 +4373,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4552,7 +4419,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4598,7 +4465,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4644,7 +4511,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4690,7 +4557,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4736,7 +4603,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4782,7 +4649,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4828,7 +4695,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4874,7 +4741,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4920,7 +4787,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4966,7 +4833,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5012,7 +4879,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5058,7 +4925,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5104,7 +4971,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5150,7 +5017,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5196,7 +5063,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5242,7 +5109,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5264,1183 +5131,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>雅盈峰 - 雅盈峰 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>99 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>91 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2520呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2523呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1608呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1254呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="17" t="inlineStr"/>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1608呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1254呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1608呎 (4+房)
-$10,323万
-$64,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1254呎 (3房)
-$7,499万
-$59,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1608呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1254呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr"/>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1608呎 (4+房)
-$9,710万
-$60,388/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1254呎 (3房)
-$9,029万
-$72,000/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1608呎 (4+房)
-$10,934万
-$68,000/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1254呎 (3房)
-$7,773万
-$61,987/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$5,043万
-$49,009/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$5,934万
-$55,255/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$4,423万
-$43,486/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr"/>
-      <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$5,094万
-$49,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$6,874万
-$64,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$4,882万
-$48,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr"/>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$4,939万
-$48,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$6,307万
-$58,724/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$5,270万
-$51,816/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr"/>
-      <c r="F16" s="17" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$4,507万
-$43,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$5,083万
-$47,326/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$4,363万
-$42,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr"/>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$4,409万
-$42,845/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$5,058万
-$47,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$4,924万
-$48,416/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr"/>
-      <c r="F18" s="17" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$4,394万
-$42,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$5,102万
-$47,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$4,832万
-$47,516/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr"/>
-      <c r="F19" s="17" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$4,322万
-$42,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$5,134万
-$47,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$4,383万
-$43,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr"/>
-      <c r="F20" s="17" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$4,296万
-$41,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$4,962万
-$46,199/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$4,261万
-$41,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr"/>
-      <c r="F21" s="17" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1029呎 (3房)
-$4,425万
-$43,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1074呎 (3房)
-$5,102万
-$47,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 1017呎 (3房)
-$4,231万
-$41,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr"/>
-      <c r="F22" s="17" t="inlineStr"/>
-      <c r="G22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,559万
-$40,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,993万
-$39,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$2,381万
-$46,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,413万
-$38,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,490万
-$39,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,486万
-$39,100/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,426万
-$38,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,955万
-$38,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$1,930万
-$37,695/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,350万
-$37,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,467万
-$38,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,459万
-$38,400/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,264万
-$35,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,864万
-$36,470/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$1,847万
-$36,080/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,197万
-$34,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,368万
-$36,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,376万
-$36,200/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,203万
-$34,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,840万
-$36,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$1,828万
-$35,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,178万
-$34,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,360万
-$35,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,368万
-$36,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,165万
-$34,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,809万
-$35,399/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$1,792万
-$35,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,134万
-$33,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,315万
-$34,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,319万
-$34,700/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,165万
-$34,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,814万
-$35,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$1,780万
-$34,766/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,140万
-$33,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,292万
-$34,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,303万
-$34,300/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,153万
-$33,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,804万
-$35,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$1,792万
-$35,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,127万
-$33,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,349万
-$35,490/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,357万
-$35,700/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,146万
-$33,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,799万
-$35,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$1,782万
-$34,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,121万
-$33,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,264万
-$33,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,281万
-$33,700/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$2,134万
-$33,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>B | 511呎 (2房)
-$1,794万
-$35,100/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 512呎 (2房)
-$1,772万
-$34,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 635呎 (2房)
-$2,108万
-$33,200/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 380呎 (1房)
-$1,250万
-$32,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>F | 380呎 (1房)
-$1,258万
-$33,100/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>A | 1055呎 (3房)
-$4,716万
-$44,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-$1,822万
-$35,800/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 510呎 (2房)
-$1,800万
-$35,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 1055呎 (3房)
-$4,610万
-$43,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr"/>
-      <c r="G32" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山-雅盈峰.xlsx
+++ b/files/港岛-半山-雅盈峰.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="雅盈峰" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +136,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +217,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5131,4 +5301,1183 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>雅盈峰 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2520呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2523呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1254呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1254呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$10323万
+$64,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1254呎 (3房)
+$7499万
+$59,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr"/>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1254呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr"/>
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$9710万
+$60,388/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1254呎 (3房)
+$9029万
+$72,000/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr"/>
+      <c r="E11" s="21" t="inlineStr"/>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1608呎 (4+房)
+$10934万
+$68,000/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1254呎 (3房)
+$7773万
+$61,987/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr"/>
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$5043万
+$49,009/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$5934万
+$55,255/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$4423万
+$43,486/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$5094万
+$49,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$6874万
+$64,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$4882万
+$48,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr"/>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$4939万
+$48,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$6307万
+$58,724/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$5270万
+$51,816/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr"/>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$4507万
+$43,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$5083万
+$47,326/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$4363万
+$42,900/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr"/>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$4409万
+$42,845/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$5058万
+$47,095/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$4924万
+$48,416/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr"/>
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$4394万
+$42,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$5102万
+$47,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$4832万
+$47,516/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr"/>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$4322万
+$42,000/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$5134万
+$47,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$4383万
+$43,100/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr"/>
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$4296万
+$41,750/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$4962万
+$46,199/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$4261万
+$41,900/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr"/>
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1029呎 (3房)
+$4425万
+$43,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1074呎 (3房)
+$5102万
+$47,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 1017呎 (3房)
+$4231万
+$41,600/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr"/>
+      <c r="F21" s="21" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2559万
+$40,300/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1993万
+$39,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$2381万
+$46,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2413万
+$38,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1490万
+$39,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1486万
+$39,100/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2426万
+$38,200/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1955万
+$38,250/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$1930万
+$37,695/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2350万
+$37,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1467万
+$38,600/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1459万
+$38,400/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2264万
+$35,650/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1864万
+$36,470/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$1847万
+$36,080/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2197万
+$34,600/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1368万
+$36,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1376万
+$36,200/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2203万
+$34,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1840万
+$36,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$1828万
+$35,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2178万
+$34,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1360万
+$35,800/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1368万
+$36,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2165万
+$34,099/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1809万
+$35,399/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$1792万
+$35,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2134万
+$33,600/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1315万
+$34,600/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1319万
+$34,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2165万
+$34,100/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1814万
+$35,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$1780万
+$34,766/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2140万
+$33,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1292万
+$34,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1303万
+$34,300/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2153万
+$33,900/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1804万
+$35,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$1792万
+$35,000/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2127万
+$33,500/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1349万
+$35,490/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1357万
+$35,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2146万
+$33,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1799万
+$35,200/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$1782万
+$34,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2121万
+$33,400/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1264万
+$33,250/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1281万
+$33,700/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$2134万
+$33,600/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B | 511呎 (2房)
+$1794万
+$35,100/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 512呎 (2房)
+$1772万
+$34,600/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 635呎 (2房)
+$2108万
+$33,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 380呎 (1房)
+$1250万
+$32,900/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 380呎 (1房)
+$1258万
+$33,100/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A | 1055呎 (3房)
+$4716万
+$44,700/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+$1822万
+$35,800/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 510呎 (2房)
+$1800万
+$35,300/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 1055呎 (3房)
+$4610万
+$43,700/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr"/>
+      <c r="G31" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山-雅盈峰.xlsx
+++ b/files/港岛-半山-雅盈峰.xlsx
@@ -644,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山-雅盈峰.xlsx
+++ b/files/港岛-半山-雅盈峰.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -704,6 +708,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -754,6 +778,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -804,6 +848,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -854,6 +918,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -904,6 +988,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -954,6 +1058,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1004,6 +1128,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1050,6 +1194,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1096,6 +1260,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1146,6 +1330,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1196,6 +1400,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1242,6 +1466,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1288,6 +1532,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1334,6 +1598,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1380,6 +1664,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1426,6 +1730,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1472,6 +1796,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1518,6 +1862,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1564,6 +1928,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1610,6 +1994,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1656,6 +2060,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1702,6 +2126,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1748,6 +2192,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1794,6 +2258,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1840,6 +2324,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1886,6 +2390,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1932,6 +2456,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1978,6 +2522,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2024,6 +2588,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2070,6 +2654,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2116,6 +2720,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2162,6 +2786,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2208,6 +2852,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2254,6 +2918,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2300,6 +2984,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2346,6 +3050,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2392,6 +3116,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2438,6 +3182,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2484,6 +3248,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2530,6 +3314,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2576,6 +3380,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2622,6 +3446,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2668,6 +3512,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2714,6 +3578,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2760,6 +3644,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2806,6 +3710,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2852,6 +3776,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2898,6 +3842,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2944,6 +3908,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2990,6 +3974,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3036,6 +4040,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3082,6 +4106,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3128,6 +4172,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3174,6 +4238,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3220,6 +4304,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3266,6 +4370,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3312,6 +4436,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3358,6 +4502,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3404,6 +4568,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3450,6 +4634,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3496,6 +4700,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3542,6 +4766,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3588,6 +4832,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3634,6 +4898,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3680,6 +4964,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3726,6 +5030,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3772,6 +5096,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3818,6 +5162,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3864,6 +5228,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3910,6 +5294,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3956,6 +5360,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4002,6 +5426,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4048,6 +5492,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4094,6 +5558,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4140,6 +5624,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4186,6 +5690,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4232,6 +5756,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4278,6 +5822,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4324,6 +5888,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4370,6 +5954,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4416,6 +6020,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4462,6 +6086,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4508,6 +6152,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4554,6 +6218,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4600,6 +6284,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4646,6 +6350,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4692,6 +6416,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4738,6 +6482,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4784,6 +6548,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4830,6 +6614,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4876,6 +6680,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4922,6 +6746,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4968,6 +6812,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5014,6 +6878,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5060,6 +6944,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5106,6 +7010,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5152,6 +7076,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5198,6 +7142,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5244,6 +7208,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5290,13 +7274,33 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5534,7 +7538,7 @@
           <t>A | 1608呎 (4+房)
 $10323万
 $64,200/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -5542,7 +7546,7 @@
           <t>B | 1254呎 (3房)
 $7499万
 $59,800/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>
@@ -5588,7 +7592,7 @@
           <t>A | 1608呎 (4+房)
 $9710万
 $60,388/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -5596,7 +7600,7 @@
           <t>B | 1254呎 (3房)
 $9029万
 $72,000/呎
-(26年-07月)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr"/>
@@ -5615,7 +7619,7 @@
           <t>A | 1608呎 (4+房)
 $10934万
 $68,000/呎
-(26年-06月)</t>
+(26年-06月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -5623,7 +7627,7 @@
           <t>B | 1254呎 (3房)
 $7773万
 $61,987/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr"/>
@@ -5642,7 +7646,7 @@
           <t>A | 1029呎 (3房)
 $5043万
 $49,009/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -5650,7 +7654,7 @@
           <t>B | 1074呎 (3房)
 $5934万
 $55,255/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -5658,7 +7662,7 @@
           <t>C | 1017呎 (3房)
 $4423万
 $43,486/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -5676,7 +7680,7 @@
           <t>A | 1029呎 (3房)
 $5094万
 $49,500/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -5684,7 +7688,7 @@
           <t>B | 1074呎 (3房)
 $6874万
 $64,000/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -5692,7 +7696,7 @@
           <t>C | 1017呎 (3房)
 $4882万
 $48,000/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -5710,7 +7714,7 @@
           <t>A | 1029呎 (3房)
 $4939万
 $48,000/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -5718,7 +7722,7 @@
           <t>B | 1074呎 (3房)
 $6307万
 $58,724/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5726,7 +7730,7 @@
           <t>C | 1017呎 (3房)
 $5270万
 $51,816/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr"/>
@@ -5744,7 +7748,7 @@
           <t>A | 1029呎 (3房)
 $4507万
 $43,800/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -5752,7 +7756,7 @@
           <t>B | 1074呎 (3房)
 $5083万
 $47,326/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5760,7 +7764,7 @@
           <t>C | 1017呎 (3房)
 $4363万
 $42,900/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr"/>
@@ -5778,7 +7782,7 @@
           <t>A | 1029呎 (3房)
 $4409万
 $42,845/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -5786,7 +7790,7 @@
           <t>B | 1074呎 (3房)
 $5058万
 $47,095/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5794,7 +7798,7 @@
           <t>C | 1017呎 (3房)
 $4924万
 $48,416/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr"/>
@@ -5812,7 +7816,7 @@
           <t>A | 1029呎 (3房)
 $4394万
 $42,700/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5820,7 +7824,7 @@
           <t>B | 1074呎 (3房)
 $5102万
 $47,500/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5828,7 +7832,7 @@
           <t>C | 1017呎 (3房)
 $4832万
 $47,516/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr"/>
@@ -5846,7 +7850,7 @@
           <t>A | 1029呎 (3房)
 $4322万
 $42,000/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5854,7 +7858,7 @@
           <t>B | 1074呎 (3房)
 $5134万
 $47,800/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5862,7 +7866,7 @@
           <t>C | 1017呎 (3房)
 $4383万
 $43,100/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr"/>
@@ -5880,7 +7884,7 @@
           <t>A | 1029呎 (3房)
 $4296万
 $41,750/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -5888,7 +7892,7 @@
           <t>B | 1074呎 (3房)
 $4962万
 $46,199/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -5896,7 +7900,7 @@
           <t>C | 1017呎 (3房)
 $4261万
 $41,900/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr"/>
@@ -5914,7 +7918,7 @@
           <t>A | 1029呎 (3房)
 $4425万
 $43,000/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -5922,7 +7926,7 @@
           <t>B | 1074呎 (3房)
 $5102万
 $47,500/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5930,7 +7934,7 @@
           <t>C | 1017呎 (3房)
 $4231万
 $41,600/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr"/>
@@ -5948,7 +7952,7 @@
           <t>A | 635呎 (2房)
 $2559万
 $40,300/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -5956,7 +7960,7 @@
           <t>B | 511呎 (2房)
 $1993万
 $39,000/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -5964,7 +7968,7 @@
           <t>C | 512呎 (2房)
 $2381万
 $46,500/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -5972,7 +7976,7 @@
           <t>D | 635呎 (2房)
 $2413万
 $38,000/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -5980,7 +7984,7 @@
           <t>E | 380呎 (1房)
 $1490万
 $39,200/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -5988,7 +7992,7 @@
           <t>F | 380呎 (1房)
 $1486万
 $39,100/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -6003,7 +8007,7 @@
           <t>A | 635呎 (2房)
 $2426万
 $38,200/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -6011,7 +8015,7 @@
           <t>B | 511呎 (2房)
 $1955万
 $38,250/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -6019,7 +8023,7 @@
           <t>C | 512呎 (2房)
 $1930万
 $37,695/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -6027,7 +8031,7 @@
           <t>D | 635呎 (2房)
 $2350万
 $37,000/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -6035,7 +8039,7 @@
           <t>E | 380呎 (1房)
 $1467万
 $38,600/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -6043,7 +8047,7 @@
           <t>F | 380呎 (1房)
 $1459万
 $38,400/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -6058,7 +8062,7 @@
           <t>A | 635呎 (2房)
 $2264万
 $35,650/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -6066,7 +8070,7 @@
           <t>B | 511呎 (2房)
 $1864万
 $36,470/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -6074,7 +8078,7 @@
           <t>C | 512呎 (2房)
 $1847万
 $36,080/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -6082,7 +8086,7 @@
           <t>D | 635呎 (2房)
 $2197万
 $34,600/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -6090,7 +8094,7 @@
           <t>E | 380呎 (1房)
 $1368万
 $36,000/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -6098,7 +8102,7 @@
           <t>F | 380呎 (1房)
 $1376万
 $36,200/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -6113,7 +8117,7 @@
           <t>A | 635呎 (2房)
 $2203万
 $34,700/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -6121,7 +8125,7 @@
           <t>B | 511呎 (2房)
 $1840万
 $36,000/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -6129,7 +8133,7 @@
           <t>C | 512呎 (2房)
 $1828万
 $35,700/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -6137,7 +8141,7 @@
           <t>D | 635呎 (2房)
 $2178万
 $34,300/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -6145,7 +8149,7 @@
           <t>E | 380呎 (1房)
 $1360万
 $35,800/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -6153,7 +8157,7 @@
           <t>F | 380呎 (1房)
 $1368万
 $36,000/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -6168,7 +8172,7 @@
           <t>A | 635呎 (2房)
 $2165万
 $34,099/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -6176,7 +8180,7 @@
           <t>B | 511呎 (2房)
 $1809万
 $35,399/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -6184,7 +8188,7 @@
           <t>C | 512呎 (2房)
 $1792万
 $35,000/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -6192,7 +8196,7 @@
           <t>D | 635呎 (2房)
 $2134万
 $33,600/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -6200,7 +8204,7 @@
           <t>E | 380呎 (1房)
 $1315万
 $34,600/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -6208,7 +8212,7 @@
           <t>F | 380呎 (1房)
 $1319万
 $34,700/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -6223,7 +8227,7 @@
           <t>A | 635呎 (2房)
 $2165万
 $34,100/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -6231,7 +8235,7 @@
           <t>B | 511呎 (2房)
 $1814万
 $35,500/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -6239,7 +8243,7 @@
           <t>C | 512呎 (2房)
 $1780万
 $34,766/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -6247,7 +8251,7 @@
           <t>D | 635呎 (2房)
 $2140万
 $33,700/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -6255,7 +8259,7 @@
           <t>E | 380呎 (1房)
 $1292万
 $34,000/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -6263,7 +8267,7 @@
           <t>F | 380呎 (1房)
 $1303万
 $34,300/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -6278,7 +8282,7 @@
           <t>A | 635呎 (2房)
 $2153万
 $33,900/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -6286,7 +8290,7 @@
           <t>B | 511呎 (2房)
 $1804万
 $35,300/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -6294,7 +8298,7 @@
           <t>C | 512呎 (2房)
 $1792万
 $35,000/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -6302,7 +8306,7 @@
           <t>D | 635呎 (2房)
 $2127万
 $33,500/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -6310,7 +8314,7 @@
           <t>E | 380呎 (1房)
 $1349万
 $35,490/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -6318,7 +8322,7 @@
           <t>F | 380呎 (1房)
 $1357万
 $35,700/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -6333,7 +8337,7 @@
           <t>A | 635呎 (2房)
 $2146万
 $33,800/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -6341,7 +8345,7 @@
           <t>B | 511呎 (2房)
 $1799万
 $35,200/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -6349,7 +8353,7 @@
           <t>C | 512呎 (2房)
 $1782万
 $34,800/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -6357,7 +8361,7 @@
           <t>D | 635呎 (2房)
 $2121万
 $33,400/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -6365,7 +8369,7 @@
           <t>E | 380呎 (1房)
 $1264万
 $33,250/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -6373,7 +8377,7 @@
           <t>F | 380呎 (1房)
 $1281万
 $33,700/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -6388,7 +8392,7 @@
           <t>A | 635呎 (2房)
 $2134万
 $33,600/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -6396,7 +8400,7 @@
           <t>B | 511呎 (2房)
 $1794万
 $35,100/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -6404,7 +8408,7 @@
           <t>C | 512呎 (2房)
 $1772万
 $34,600/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -6412,7 +8416,7 @@
           <t>D | 635呎 (2房)
 $2108万
 $33,200/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -6420,7 +8424,7 @@
           <t>E | 380呎 (1房)
 $1250万
 $32,900/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -6428,7 +8432,7 @@
           <t>F | 380呎 (1房)
 $1258万
 $33,100/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -6443,7 +8447,7 @@
           <t>A | 1055呎 (3房)
 $4716万
 $44,700/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -6451,7 +8455,7 @@
           <t>B | 509呎 (2房)
 $1822万
 $35,800/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -6459,7 +8463,7 @@
           <t>C | 510呎 (2房)
 $1800万
 $35,300/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -6467,7 +8471,7 @@
           <t>D | 1055呎 (3房)
 $4610万
 $43,700/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr"/>

--- a/files/港岛-半山-雅盈峰.xlsx
+++ b/files/港岛-半山-雅盈峰.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -7619,7 +7619,7 @@
           <t>A | 1608呎 (4+房)
 $10934万
 $68,000/呎
-(26年-06月-20日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">

--- a/files/港岛-半山-雅盈峰.xlsx
+++ b/files/港岛-半山-雅盈峰.xlsx
@@ -7538,7 +7538,7 @@
           <t>A | 1608呎 (4+房)
 $10323万
 $64,200/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -7546,7 +7546,7 @@
           <t>B | 1254呎 (3房)
 $7499万
 $59,800/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>
@@ -7592,7 +7592,7 @@
           <t>A | 1608呎 (4+房)
 $9710万
 $60,388/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7600,7 +7600,7 @@
           <t>B | 1254呎 (3房)
 $9029万
 $72,000/呎
-(26年-07月-03日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr"/>
@@ -7619,7 +7619,7 @@
           <t>A | 1608呎 (4+房)
 $10934万
 $68,000/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -7627,7 +7627,7 @@
           <t>B | 1254呎 (3房)
 $7773万
 $61,987/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
           <t>A | 1029呎 (3房)
 $5043万
 $49,009/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -7654,7 +7654,7 @@
           <t>B | 1074呎 (3房)
 $5934万
 $55,255/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -7662,7 +7662,7 @@
           <t>C | 1017呎 (3房)
 $4423万
 $43,486/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -7680,7 +7680,7 @@
           <t>A | 1029呎 (3房)
 $5094万
 $49,500/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7688,7 +7688,7 @@
           <t>B | 1074呎 (3房)
 $6874万
 $64,000/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7696,7 +7696,7 @@
           <t>C | 1017呎 (3房)
 $4882万
 $48,000/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -7714,7 +7714,7 @@
           <t>A | 1029呎 (3房)
 $4939万
 $48,000/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7722,7 +7722,7 @@
           <t>B | 1074呎 (3房)
 $6307万
 $58,724/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -7730,7 +7730,7 @@
           <t>C | 1017呎 (3房)
 $5270万
 $51,816/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr"/>
@@ -7748,7 +7748,7 @@
           <t>A | 1029呎 (3房)
 $4507万
 $43,800/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7756,7 +7756,7 @@
           <t>B | 1074呎 (3房)
 $5083万
 $47,326/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -7764,7 +7764,7 @@
           <t>C | 1017呎 (3房)
 $4363万
 $42,900/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr"/>
@@ -7782,7 +7782,7 @@
           <t>A | 1029呎 (3房)
 $4409万
 $42,845/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7790,7 +7790,7 @@
           <t>B | 1074呎 (3房)
 $5058万
 $47,095/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -7798,7 +7798,7 @@
           <t>C | 1017呎 (3房)
 $4924万
 $48,416/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr"/>
@@ -7816,7 +7816,7 @@
           <t>A | 1029呎 (3房)
 $4394万
 $42,700/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7824,7 +7824,7 @@
           <t>B | 1074呎 (3房)
 $5102万
 $47,500/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7832,7 +7832,7 @@
           <t>C | 1017呎 (3房)
 $4832万
 $47,516/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr"/>
@@ -7850,7 +7850,7 @@
           <t>A | 1029呎 (3房)
 $4322万
 $42,000/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7858,7 +7858,7 @@
           <t>B | 1074呎 (3房)
 $5134万
 $47,800/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7866,7 +7866,7 @@
           <t>C | 1017呎 (3房)
 $4383万
 $43,100/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr"/>
@@ -7884,7 +7884,7 @@
           <t>A | 1029呎 (3房)
 $4296万
 $41,750/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7892,7 +7892,7 @@
           <t>B | 1074呎 (3房)
 $4962万
 $46,199/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -7900,7 +7900,7 @@
           <t>C | 1017呎 (3房)
 $4261万
 $41,900/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr"/>
@@ -7918,7 +7918,7 @@
           <t>A | 1029呎 (3房)
 $4425万
 $43,000/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7926,7 +7926,7 @@
           <t>B | 1074呎 (3房)
 $5102万
 $47,500/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7934,7 +7934,7 @@
           <t>C | 1017呎 (3房)
 $4231万
 $41,600/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
           <t>A | 635呎 (2房)
 $2559万
 $40,300/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -7960,7 +7960,7 @@
           <t>B | 511呎 (2房)
 $1993万
 $39,000/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -7968,7 +7968,7 @@
           <t>C | 512呎 (2房)
 $2381万
 $46,500/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7976,7 +7976,7 @@
           <t>D | 635呎 (2房)
 $2413万
 $38,000/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -7984,7 +7984,7 @@
           <t>E | 380呎 (1房)
 $1490万
 $39,200/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -7992,7 +7992,7 @@
           <t>F | 380呎 (1房)
 $1486万
 $39,100/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
           <t>A | 635呎 (2房)
 $2426万
 $38,200/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -8015,7 +8015,7 @@
           <t>B | 511呎 (2房)
 $1955万
 $38,250/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -8023,7 +8023,7 @@
           <t>C | 512呎 (2房)
 $1930万
 $37,695/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -8031,7 +8031,7 @@
           <t>D | 635呎 (2房)
 $2350万
 $37,000/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -8039,7 +8039,7 @@
           <t>E | 380呎 (1房)
 $1467万
 $38,600/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -8047,7 +8047,7 @@
           <t>F | 380呎 (1房)
 $1459万
 $38,400/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
           <t>A | 635呎 (2房)
 $2264万
 $35,650/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -8070,7 +8070,7 @@
           <t>B | 511呎 (2房)
 $1864万
 $36,470/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -8078,7 +8078,7 @@
           <t>C | 512呎 (2房)
 $1847万
 $36,080/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -8086,7 +8086,7 @@
           <t>D | 635呎 (2房)
 $2197万
 $34,600/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -8094,7 +8094,7 @@
           <t>E | 380呎 (1房)
 $1368万
 $36,000/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -8102,7 +8102,7 @@
           <t>F | 380呎 (1房)
 $1376万
 $36,200/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
           <t>A | 635呎 (2房)
 $2203万
 $34,700/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -8125,7 +8125,7 @@
           <t>B | 511呎 (2房)
 $1840万
 $36,000/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -8133,7 +8133,7 @@
           <t>C | 512呎 (2房)
 $1828万
 $35,700/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -8141,7 +8141,7 @@
           <t>D | 635呎 (2房)
 $2178万
 $34,300/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -8149,7 +8149,7 @@
           <t>E | 380呎 (1房)
 $1360万
 $35,800/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -8157,7 +8157,7 @@
           <t>F | 380呎 (1房)
 $1368万
 $36,000/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
           <t>A | 635呎 (2房)
 $2165万
 $34,099/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -8180,7 +8180,7 @@
           <t>B | 511呎 (2房)
 $1809万
 $35,399/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -8188,7 +8188,7 @@
           <t>C | 512呎 (2房)
 $1792万
 $35,000/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -8196,7 +8196,7 @@
           <t>D | 635呎 (2房)
 $2134万
 $33,600/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -8204,7 +8204,7 @@
           <t>E | 380呎 (1房)
 $1315万
 $34,600/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -8212,7 +8212,7 @@
           <t>F | 380呎 (1房)
 $1319万
 $34,700/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
           <t>A | 635呎 (2房)
 $2165万
 $34,100/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -8235,7 +8235,7 @@
           <t>B | 511呎 (2房)
 $1814万
 $35,500/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -8243,7 +8243,7 @@
           <t>C | 512呎 (2房)
 $1780万
 $34,766/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -8251,7 +8251,7 @@
           <t>D | 635呎 (2房)
 $2140万
 $33,700/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -8259,7 +8259,7 @@
           <t>E | 380呎 (1房)
 $1292万
 $34,000/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -8267,7 +8267,7 @@
           <t>F | 380呎 (1房)
 $1303万
 $34,300/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
           <t>A | 635呎 (2房)
 $2153万
 $33,900/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -8290,7 +8290,7 @@
           <t>B | 511呎 (2房)
 $1804万
 $35,300/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -8298,7 +8298,7 @@
           <t>C | 512呎 (2房)
 $1792万
 $35,000/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -8306,7 +8306,7 @@
           <t>D | 635呎 (2房)
 $2127万
 $33,500/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -8314,7 +8314,7 @@
           <t>E | 380呎 (1房)
 $1349万
 $35,490/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -8322,7 +8322,7 @@
           <t>F | 380呎 (1房)
 $1357万
 $35,700/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
           <t>A | 635呎 (2房)
 $2146万
 $33,800/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -8345,7 +8345,7 @@
           <t>B | 511呎 (2房)
 $1799万
 $35,200/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -8353,7 +8353,7 @@
           <t>C | 512呎 (2房)
 $1782万
 $34,800/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -8361,7 +8361,7 @@
           <t>D | 635呎 (2房)
 $2121万
 $33,400/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -8369,7 +8369,7 @@
           <t>E | 380呎 (1房)
 $1264万
 $33,250/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -8377,7 +8377,7 @@
           <t>F | 380呎 (1房)
 $1281万
 $33,700/呎
-(26年-03月-15日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
           <t>A | 635呎 (2房)
 $2134万
 $33,600/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -8400,7 +8400,7 @@
           <t>B | 511呎 (2房)
 $1794万
 $35,100/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -8408,7 +8408,7 @@
           <t>C | 512呎 (2房)
 $1772万
 $34,600/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -8416,7 +8416,7 @@
           <t>D | 635呎 (2房)
 $2108万
 $33,200/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -8424,7 +8424,7 @@
           <t>E | 380呎 (1房)
 $1250万
 $32,900/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -8432,7 +8432,7 @@
           <t>F | 380呎 (1房)
 $1258万
 $33,100/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
           <t>A | 1055呎 (3房)
 $4716万
 $44,700/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -8455,7 +8455,7 @@
           <t>B | 509呎 (2房)
 $1822万
 $35,800/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -8463,7 +8463,7 @@
           <t>C | 510呎 (2房)
 $1800万
 $35,300/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -8471,7 +8471,7 @@
           <t>D | 1055呎 (3房)
 $4610万
 $43,700/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr"/>

--- a/files/港岛-半山-雅盈峰.xlsx
+++ b/files/港岛-半山-雅盈峰.xlsx
@@ -7538,7 +7538,7 @@
           <t>A | 1608呎 (4+房)
 $10323万
 $64,200/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -7546,7 +7546,7 @@
           <t>B | 1254呎 (3房)
 $7499万
 $59,800/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr"/>
@@ -7592,7 +7592,7 @@
           <t>A | 1608呎 (4+房)
 $9710万
 $60,388/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7600,7 +7600,7 @@
           <t>B | 1254呎 (3房)
 $9029万
 $72,000/呎
-(26年-07月)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr"/>
@@ -7619,7 +7619,7 @@
           <t>A | 1608呎 (4+房)
 $10934万
 $68,000/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -7627,7 +7627,7 @@
           <t>B | 1254呎 (3房)
 $7773万
 $61,987/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
           <t>A | 1029呎 (3房)
 $5043万
 $49,009/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -7654,7 +7654,7 @@
           <t>B | 1074呎 (3房)
 $5934万
 $55,255/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -7662,7 +7662,7 @@
           <t>C | 1017呎 (3房)
 $4423万
 $43,486/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -7680,7 +7680,7 @@
           <t>A | 1029呎 (3房)
 $5094万
 $49,500/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7688,7 +7688,7 @@
           <t>B | 1074呎 (3房)
 $6874万
 $64,000/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7696,7 +7696,7 @@
           <t>C | 1017呎 (3房)
 $4882万
 $48,000/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr"/>
@@ -7714,7 +7714,7 @@
           <t>A | 1029呎 (3房)
 $4939万
 $48,000/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7722,7 +7722,7 @@
           <t>B | 1074呎 (3房)
 $6307万
 $58,724/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -7730,7 +7730,7 @@
           <t>C | 1017呎 (3房)
 $5270万
 $51,816/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr"/>
@@ -7748,7 +7748,7 @@
           <t>A | 1029呎 (3房)
 $4507万
 $43,800/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7756,7 +7756,7 @@
           <t>B | 1074呎 (3房)
 $5083万
 $47,326/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -7764,7 +7764,7 @@
           <t>C | 1017呎 (3房)
 $4363万
 $42,900/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr"/>
@@ -7782,7 +7782,7 @@
           <t>A | 1029呎 (3房)
 $4409万
 $42,845/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7790,7 +7790,7 @@
           <t>B | 1074呎 (3房)
 $5058万
 $47,095/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -7798,7 +7798,7 @@
           <t>C | 1017呎 (3房)
 $4924万
 $48,416/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr"/>
@@ -7816,7 +7816,7 @@
           <t>A | 1029呎 (3房)
 $4394万
 $42,700/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7824,7 +7824,7 @@
           <t>B | 1074呎 (3房)
 $5102万
 $47,500/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7832,7 +7832,7 @@
           <t>C | 1017呎 (3房)
 $4832万
 $47,516/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr"/>
@@ -7850,7 +7850,7 @@
           <t>A | 1029呎 (3房)
 $4322万
 $42,000/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7858,7 +7858,7 @@
           <t>B | 1074呎 (3房)
 $5134万
 $47,800/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7866,7 +7866,7 @@
           <t>C | 1017呎 (3房)
 $4383万
 $43,100/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr"/>
@@ -7884,7 +7884,7 @@
           <t>A | 1029呎 (3房)
 $4296万
 $41,750/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7892,7 +7892,7 @@
           <t>B | 1074呎 (3房)
 $4962万
 $46,199/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -7900,7 +7900,7 @@
           <t>C | 1017呎 (3房)
 $4261万
 $41,900/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr"/>
@@ -7918,7 +7918,7 @@
           <t>A | 1029呎 (3房)
 $4425万
 $43,000/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7926,7 +7926,7 @@
           <t>B | 1074呎 (3房)
 $5102万
 $47,500/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7934,7 +7934,7 @@
           <t>C | 1017呎 (3房)
 $4231万
 $41,600/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
           <t>A | 635呎 (2房)
 $2559万
 $40,300/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -7960,7 +7960,7 @@
           <t>B | 511呎 (2房)
 $1993万
 $39,000/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -7968,7 +7968,7 @@
           <t>C | 512呎 (2房)
 $2381万
 $46,500/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7976,7 +7976,7 @@
           <t>D | 635呎 (2房)
 $2413万
 $38,000/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -7984,7 +7984,7 @@
           <t>E | 380呎 (1房)
 $1490万
 $39,200/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -7992,7 +7992,7 @@
           <t>F | 380呎 (1房)
 $1486万
 $39,100/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
           <t>A | 635呎 (2房)
 $2426万
 $38,200/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -8015,7 +8015,7 @@
           <t>B | 511呎 (2房)
 $1955万
 $38,250/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -8023,7 +8023,7 @@
           <t>C | 512呎 (2房)
 $1930万
 $37,695/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -8031,7 +8031,7 @@
           <t>D | 635呎 (2房)
 $2350万
 $37,000/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -8039,7 +8039,7 @@
           <t>E | 380呎 (1房)
 $1467万
 $38,600/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -8047,7 +8047,7 @@
           <t>F | 380呎 (1房)
 $1459万
 $38,400/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
           <t>A | 635呎 (2房)
 $2264万
 $35,650/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -8070,7 +8070,7 @@
           <t>B | 511呎 (2房)
 $1864万
 $36,470/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -8078,7 +8078,7 @@
           <t>C | 512呎 (2房)
 $1847万
 $36,080/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -8086,7 +8086,7 @@
           <t>D | 635呎 (2房)
 $2197万
 $34,600/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -8094,7 +8094,7 @@
           <t>E | 380呎 (1房)
 $1368万
 $36,000/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -8102,7 +8102,7 @@
           <t>F | 380呎 (1房)
 $1376万
 $36,200/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -8117,7 +8117,7 @@
           <t>A | 635呎 (2房)
 $2203万
 $34,700/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -8125,7 +8125,7 @@
           <t>B | 511呎 (2房)
 $1840万
 $36,000/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -8133,7 +8133,7 @@
           <t>C | 512呎 (2房)
 $1828万
 $35,700/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -8141,7 +8141,7 @@
           <t>D | 635呎 (2房)
 $2178万
 $34,300/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -8149,7 +8149,7 @@
           <t>E | 380呎 (1房)
 $1360万
 $35,800/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -8157,7 +8157,7 @@
           <t>F | 380呎 (1房)
 $1368万
 $36,000/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
           <t>A | 635呎 (2房)
 $2165万
 $34,099/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -8180,7 +8180,7 @@
           <t>B | 511呎 (2房)
 $1809万
 $35,399/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -8188,7 +8188,7 @@
           <t>C | 512呎 (2房)
 $1792万
 $35,000/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -8196,7 +8196,7 @@
           <t>D | 635呎 (2房)
 $2134万
 $33,600/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -8204,7 +8204,7 @@
           <t>E | 380呎 (1房)
 $1315万
 $34,600/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -8212,7 +8212,7 @@
           <t>F | 380呎 (1房)
 $1319万
 $34,700/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
           <t>A | 635呎 (2房)
 $2165万
 $34,100/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -8235,7 +8235,7 @@
           <t>B | 511呎 (2房)
 $1814万
 $35,500/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -8243,7 +8243,7 @@
           <t>C | 512呎 (2房)
 $1780万
 $34,766/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -8251,7 +8251,7 @@
           <t>D | 635呎 (2房)
 $2140万
 $33,700/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -8259,7 +8259,7 @@
           <t>E | 380呎 (1房)
 $1292万
 $34,000/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -8267,7 +8267,7 @@
           <t>F | 380呎 (1房)
 $1303万
 $34,300/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
           <t>A | 635呎 (2房)
 $2153万
 $33,900/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -8290,7 +8290,7 @@
           <t>B | 511呎 (2房)
 $1804万
 $35,300/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -8298,7 +8298,7 @@
           <t>C | 512呎 (2房)
 $1792万
 $35,000/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -8306,7 +8306,7 @@
           <t>D | 635呎 (2房)
 $2127万
 $33,500/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -8314,7 +8314,7 @@
           <t>E | 380呎 (1房)
 $1349万
 $35,490/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -8322,7 +8322,7 @@
           <t>F | 380呎 (1房)
 $1357万
 $35,700/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
           <t>A | 635呎 (2房)
 $2146万
 $33,800/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -8345,7 +8345,7 @@
           <t>B | 511呎 (2房)
 $1799万
 $35,200/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -8353,7 +8353,7 @@
           <t>C | 512呎 (2房)
 $1782万
 $34,800/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -8361,7 +8361,7 @@
           <t>D | 635呎 (2房)
 $2121万
 $33,400/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -8369,7 +8369,7 @@
           <t>E | 380呎 (1房)
 $1264万
 $33,250/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -8377,7 +8377,7 @@
           <t>F | 380呎 (1房)
 $1281万
 $33,700/呎
-(26年-03月)</t>
+(26年-03月-15日)</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
           <t>A | 635呎 (2房)
 $2134万
 $33,600/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -8400,7 +8400,7 @@
           <t>B | 511呎 (2房)
 $1794万
 $35,100/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -8408,7 +8408,7 @@
           <t>C | 512呎 (2房)
 $1772万
 $34,600/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -8416,7 +8416,7 @@
           <t>D | 635呎 (2房)
 $2108万
 $33,200/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -8424,7 +8424,7 @@
           <t>E | 380呎 (1房)
 $1250万
 $32,900/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -8432,7 +8432,7 @@
           <t>F | 380呎 (1房)
 $1258万
 $33,100/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
           <t>A | 1055呎 (3房)
 $4716万
 $44,700/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -8455,7 +8455,7 @@
           <t>B | 509呎 (2房)
 $1822万
 $35,800/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -8463,7 +8463,7 @@
           <t>C | 510呎 (2房)
 $1800万
 $35,300/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -8471,7 +8471,7 @@
           <t>D | 1055呎 (3房)
 $4610万
 $43,700/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr"/>
